--- a/dados_cafe.xlsx
+++ b/dados_cafe.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7403566dc7686ca4/cHALLENGE lek/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7403566dc7686ca4/Dados Desafio LEK/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70C486DF-C364-4564-A835-5A3E7B5FA8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{70C486DF-C364-4564-A835-5A3E7B5FA8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC597355-381E-4378-91B8-864A571A5750}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{582FE47F-9B16-4A79-AFD0-F41D506ACDC2}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="39">
   <si>
     <t>Commodity</t>
   </si>
@@ -635,13 +635,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1124,888 +1121,922 @@
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>34.1</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>35.1</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>53.6</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>33.200000000000003</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="2">
         <v>43.6</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="2">
         <v>36.1</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="2">
         <v>46.7</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="2">
         <v>39.1</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="2">
         <v>53.3</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="2">
         <v>44.8</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="2">
         <v>54.5</v>
       </c>
-      <c r="O2" s="3">
+      <c r="O2" s="2">
         <v>49.2</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="2">
         <v>57.6</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="2">
         <v>57.2</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="2">
         <v>54.3</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="2">
         <v>49.4</v>
       </c>
-      <c r="T2" s="3">
+      <c r="T2" s="2">
         <v>56.1</v>
       </c>
-      <c r="U2" s="3">
+      <c r="U2" s="2">
         <v>52.1</v>
       </c>
-      <c r="V2" s="3">
+      <c r="V2" s="2">
         <v>66.5</v>
       </c>
-      <c r="W2" s="3">
+      <c r="W2" s="2">
         <v>60.5</v>
       </c>
-      <c r="X2" s="3">
+      <c r="X2" s="2">
         <v>69.900000000000006</v>
       </c>
-      <c r="Y2" s="3">
+      <c r="Y2" s="2">
         <v>58.1</v>
       </c>
-      <c r="Z2" s="3">
+      <c r="Z2" s="2">
         <v>62.6</v>
       </c>
-      <c r="AA2" s="3">
+      <c r="AA2" s="2">
         <v>66.3</v>
       </c>
-      <c r="AB2" s="3">
+      <c r="AB2" s="2">
         <v>65</v>
       </c>
-      <c r="AC2" s="3">
+      <c r="AC2" s="2">
         <v>63</v>
       </c>
-      <c r="AD2" s="3" t="s">
+      <c r="AD2" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
+      <c r="A3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>0</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>0</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>0</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <v>0</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <v>0</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="2">
         <v>0</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="2">
         <v>0</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="2">
         <v>0</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="2">
         <v>0</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="2">
         <v>0</v>
       </c>
-      <c r="O3" s="3">
+      <c r="O3" s="2">
         <v>0</v>
       </c>
-      <c r="P3" s="3">
+      <c r="P3" s="2">
         <v>0</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="Q3" s="2">
         <v>34</v>
       </c>
-      <c r="R3" s="3">
+      <c r="R3" s="2">
         <v>52</v>
       </c>
-      <c r="S3" s="3">
+      <c r="S3" s="2">
         <v>65</v>
       </c>
-      <c r="T3" s="3">
+      <c r="T3" s="2">
         <v>62</v>
       </c>
-      <c r="U3" s="3">
+      <c r="U3" s="2">
         <v>61</v>
       </c>
-      <c r="V3" s="3">
+      <c r="V3" s="2">
         <v>67</v>
       </c>
-      <c r="W3" s="3">
+      <c r="W3" s="2">
         <v>67</v>
       </c>
-      <c r="X3" s="3">
+      <c r="X3" s="2">
         <v>72</v>
       </c>
-      <c r="Y3" s="3">
+      <c r="Y3" s="2">
         <v>75</v>
       </c>
-      <c r="Z3" s="3">
+      <c r="Z3" s="2">
         <v>75</v>
       </c>
-      <c r="AA3" s="3">
+      <c r="AA3" s="2">
         <v>75</v>
       </c>
-      <c r="AB3" s="3">
+      <c r="AB3" s="2">
         <v>75</v>
       </c>
-      <c r="AC3" s="3">
+      <c r="AC3" s="2">
         <v>75</v>
       </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AD3" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3" t="s">
+      <c r="A4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>19.675999999999998</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>24.795000000000002</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>29.396000000000001</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>24.92</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <v>27.92</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="2">
         <v>24.542999999999999</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <v>29.26</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="2">
         <v>27.29</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="2">
         <v>31.475000000000001</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="2">
         <v>29.78</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="2">
         <v>35.01</v>
       </c>
-      <c r="O4" s="3">
+      <c r="O4" s="2">
         <v>29.843</v>
       </c>
-      <c r="P4" s="3">
+      <c r="P4" s="2">
         <v>30.66</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="Q4" s="2">
         <v>34.146000000000001</v>
       </c>
-      <c r="R4" s="3">
+      <c r="R4" s="2">
         <v>36.573</v>
       </c>
-      <c r="S4" s="3">
+      <c r="S4" s="2">
         <v>35.542999999999999</v>
       </c>
-      <c r="T4" s="3">
+      <c r="T4" s="2">
         <v>33.081000000000003</v>
       </c>
-      <c r="U4" s="3">
+      <c r="U4" s="2">
         <v>30.454000000000001</v>
       </c>
-      <c r="V4" s="3">
+      <c r="V4" s="2">
         <v>41.426000000000002</v>
       </c>
-      <c r="W4" s="3">
+      <c r="W4" s="2">
         <v>40.256</v>
       </c>
-      <c r="X4" s="3">
+      <c r="X4" s="2">
         <v>45.674999999999997</v>
       </c>
-      <c r="Y4" s="3">
+      <c r="Y4" s="2">
         <v>39.685000000000002</v>
       </c>
-      <c r="Z4" s="3">
+      <c r="Z4" s="2">
         <v>36.145000000000003</v>
       </c>
-      <c r="AA4" s="3">
+      <c r="AA4" s="2">
         <v>46.75</v>
       </c>
-      <c r="AB4" s="3">
+      <c r="AB4" s="2">
         <v>44.75</v>
       </c>
-      <c r="AC4" s="3">
+      <c r="AC4" s="2">
         <v>40.75</v>
       </c>
-      <c r="AD4" s="3" t="s">
+      <c r="AD4" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3" t="s">
+      <c r="A5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>13.1</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>13.7</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>13.5</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>14.4</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <v>15.5</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <v>15.914999999999999</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <v>16.72</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="2">
         <v>17.39</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="2">
         <v>18.03</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="2">
         <v>18.760000000000002</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="2">
         <v>19.420000000000002</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5" s="2">
         <v>20.024999999999999</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="2">
         <v>20.11</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="2">
         <v>20.21</v>
       </c>
-      <c r="R5" s="3">
+      <c r="R5" s="2">
         <v>20.420000000000002</v>
       </c>
-      <c r="S5" s="3">
+      <c r="S5" s="2">
         <v>20.855</v>
       </c>
-      <c r="T5" s="3">
+      <c r="T5" s="2">
         <v>21.625</v>
       </c>
-      <c r="U5" s="3">
+      <c r="U5" s="2">
         <v>22.42</v>
       </c>
-      <c r="V5" s="3">
+      <c r="V5" s="2">
         <v>23.2</v>
       </c>
-      <c r="W5" s="3">
+      <c r="W5" s="2">
         <v>22.994</v>
       </c>
-      <c r="X5" s="3">
+      <c r="X5" s="2">
         <v>22.28</v>
       </c>
-      <c r="Y5" s="3">
+      <c r="Y5" s="2">
         <v>22.34</v>
       </c>
-      <c r="Z5" s="3">
+      <c r="Z5" s="2">
         <v>22.45</v>
       </c>
-      <c r="AA5" s="3">
+      <c r="AA5" s="2">
         <v>22.16</v>
       </c>
-      <c r="AB5" s="3">
+      <c r="AB5" s="2">
         <v>21.97</v>
       </c>
-      <c r="AC5" s="3">
+      <c r="AC5" s="2">
         <v>22.28</v>
       </c>
-      <c r="AD5" s="3" t="s">
+      <c r="AD5" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>10.63</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>7.2350000000000003</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>17.939</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <v>11.819000000000001</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="2">
         <v>11.999000000000001</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="2">
         <v>7.641</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="2">
         <v>8.3610000000000007</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="2">
         <v>2.7810000000000001</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="2">
         <v>6.5759999999999996</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="2">
         <v>2.8359999999999999</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="2">
         <v>2.9060000000000001</v>
       </c>
-      <c r="O6" s="3">
+      <c r="O6" s="2">
         <v>2.238</v>
       </c>
-      <c r="P6" s="3">
+      <c r="P6" s="2">
         <v>9.0679999999999996</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="Q6" s="2">
         <v>11.946</v>
       </c>
-      <c r="R6" s="3">
+      <c r="R6" s="2">
         <v>9.3049999999999997</v>
       </c>
-      <c r="S6" s="3">
+      <c r="S6" s="2">
         <v>2.3719999999999999</v>
       </c>
-      <c r="T6" s="3">
+      <c r="T6" s="2">
         <v>3.8279999999999998</v>
       </c>
-      <c r="U6" s="3">
+      <c r="U6" s="2">
         <v>3.1150000000000002</v>
       </c>
-      <c r="V6" s="3">
+      <c r="V6" s="2">
         <v>5.056</v>
       </c>
-      <c r="W6" s="3">
+      <c r="W6" s="2">
         <v>2.3730000000000002</v>
       </c>
-      <c r="X6" s="3">
+      <c r="X6" s="2">
         <v>4.3899999999999997</v>
       </c>
-      <c r="Y6" s="3">
+      <c r="Y6" s="2">
         <v>540</v>
       </c>
-      <c r="Z6" s="3">
+      <c r="Z6" s="2">
         <v>4.62</v>
       </c>
-      <c r="AA6" s="3">
+      <c r="AA6" s="2">
         <v>2.085</v>
       </c>
-      <c r="AB6" s="3">
+      <c r="AB6" s="2">
         <v>440</v>
       </c>
-      <c r="AC6" s="3">
+      <c r="AC6" s="2">
         <v>485</v>
       </c>
-      <c r="AD6" s="3" t="s">
+      <c r="AD6" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>117.217</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>111.625</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>127.292</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <v>111.282</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <v>121.946</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="2">
         <v>117.883</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="2">
         <v>134.05000000000001</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="2">
         <v>124.38800000000001</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="2">
         <v>136.751</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="2">
         <v>129.774</v>
       </c>
-      <c r="N7" s="3">
+      <c r="N7" s="2">
         <v>141.40899999999999</v>
       </c>
-      <c r="O7" s="3">
+      <c r="O7" s="2">
         <v>144.83699999999999</v>
       </c>
-      <c r="P7" s="3">
+      <c r="P7" s="2">
         <v>158.018</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="Q7" s="2">
         <v>160.054</v>
       </c>
-      <c r="R7" s="3">
+      <c r="R7" s="2">
         <v>153.79599999999999</v>
       </c>
-      <c r="S7" s="3">
+      <c r="S7" s="2">
         <v>152.429</v>
       </c>
-      <c r="T7" s="3">
+      <c r="T7" s="2">
         <v>161.07900000000001</v>
       </c>
-      <c r="U7" s="3">
+      <c r="U7" s="2">
         <v>159.81399999999999</v>
       </c>
-      <c r="V7" s="3">
+      <c r="V7" s="2">
         <v>175.85599999999999</v>
       </c>
-      <c r="W7" s="3">
+      <c r="W7" s="2">
         <v>169.03</v>
       </c>
-      <c r="X7" s="3">
+      <c r="X7" s="2">
         <v>176.54900000000001</v>
       </c>
-      <c r="Y7" s="3">
+      <c r="Y7" s="2">
         <v>165.04400000000001</v>
       </c>
-      <c r="Z7" s="3">
+      <c r="Z7" s="2">
         <v>164.38900000000001</v>
       </c>
-      <c r="AA7" s="3">
+      <c r="AA7" s="2">
         <v>169.345</v>
       </c>
-      <c r="AB7" s="3">
+      <c r="AB7" s="2">
         <v>175.316</v>
       </c>
-      <c r="AC7" s="3">
+      <c r="AC7" s="2">
         <v>178.84800000000001</v>
       </c>
-      <c r="AD7" s="3" t="s">
+      <c r="AD7" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3" t="s">
+      <c r="A8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>1.488</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>7.0940000000000003</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>90.376000000000005</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <v>90.385000000000005</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="2">
         <v>91.483999999999995</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="2">
         <v>94.218999999999994</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="2">
         <v>100.514</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="2">
         <v>101.583</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="2">
         <v>101.735</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="2">
         <v>105.458</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N8" s="2">
         <v>110.866</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="2">
         <v>113.133</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="2">
         <v>118.238</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="2">
         <v>118.902</v>
       </c>
-      <c r="R8" s="3">
+      <c r="R8" s="2">
         <v>119.342</v>
       </c>
-      <c r="S8" s="3">
+      <c r="S8" s="2">
         <v>126.42100000000001</v>
       </c>
-      <c r="T8" s="3">
+      <c r="T8" s="2">
         <v>129.13300000000001</v>
       </c>
-      <c r="U8" s="3">
+      <c r="U8" s="2">
         <v>130.48500000000001</v>
       </c>
-      <c r="V8" s="3">
+      <c r="V8" s="2">
         <v>138.506</v>
       </c>
-      <c r="W8" s="3">
+      <c r="W8" s="2">
         <v>131.18799999999999</v>
       </c>
-      <c r="X8" s="3">
+      <c r="X8" s="2">
         <v>132.126</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Y8" s="2">
         <v>140.86099999999999</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="Z8" s="2">
         <v>133.91800000000001</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AA8" s="2">
         <v>134.27500000000001</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AB8" s="2">
         <v>141.79900000000001</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AC8" s="2">
         <v>143.94</v>
       </c>
-      <c r="AD8" s="3" t="s">
+      <c r="AD8" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="3" t="s">
+      <c r="A9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>90.846999999999994</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <v>88.292000000000002</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>95.462999999999994</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <v>91.938999999999993</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="2">
         <v>95.147000000000006</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="2">
         <v>95.442999999999998</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="2">
         <v>107.087</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="2">
         <v>101.361</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <v>104.434</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="2">
         <v>106.78400000000001</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="2">
         <v>116.97199999999999</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="2">
         <v>118.03100000000001</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="2">
         <v>123.239</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="2">
         <v>129.26</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="2">
         <v>124.027</v>
       </c>
-      <c r="S9" s="3">
+      <c r="S9" s="2">
         <v>133.845</v>
       </c>
-      <c r="T9" s="3">
+      <c r="T9" s="2">
         <v>133.60599999999999</v>
       </c>
-      <c r="U9" s="3">
+      <c r="U9" s="2">
         <v>134.17400000000001</v>
       </c>
-      <c r="V9" s="3">
+      <c r="V9" s="2">
         <v>143.364</v>
       </c>
-      <c r="W9" s="3">
+      <c r="W9" s="2">
         <v>139.001</v>
       </c>
-      <c r="X9" s="3">
+      <c r="X9" s="2">
         <v>144.89599999999999</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Y9" s="2">
         <v>143.57599999999999</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="Z9" s="2">
         <v>134.559</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AA9" s="2">
         <v>143.465</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AB9" s="2">
         <v>147.37299999999999</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AC9" s="2">
         <v>150.095</v>
       </c>
-      <c r="AD9" s="3" t="s">
+      <c r="AD9" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="3" t="s">
+      <c r="A10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <v>26.303000000000001</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <v>27.574999999999999</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <v>114.35899999999999</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="2">
         <v>117.59099999999999</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="2">
         <v>116.63</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="2">
         <v>125.151</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="2">
         <v>124.352</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="2">
         <v>128.90799999999999</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="2">
         <v>125.867</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="2">
         <v>139.196</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="2">
         <v>135.50800000000001</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="2">
         <v>142.83099999999999</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="2">
         <v>143.4</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="2">
         <v>143.87700000000001</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="2">
         <v>147.16300000000001</v>
       </c>
-      <c r="S10" s="3">
+      <c r="S10" s="2">
         <v>153.18600000000001</v>
       </c>
-      <c r="T10" s="3">
+      <c r="T10" s="2">
         <v>155.10400000000001</v>
       </c>
-      <c r="U10" s="3">
+      <c r="U10" s="2">
         <v>160.62700000000001</v>
       </c>
-      <c r="V10" s="3">
+      <c r="V10" s="2">
         <v>166.00299999999999</v>
       </c>
-      <c r="W10" s="3">
+      <c r="W10" s="2">
         <v>162.35499999999999</v>
       </c>
-      <c r="X10" s="3">
+      <c r="X10" s="2">
         <v>162.09299999999999</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Y10" s="2">
         <v>167.88300000000001</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="Z10" s="2">
         <v>168.75399999999999</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AA10" s="2">
         <v>163.96799999999999</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AB10" s="2">
         <v>171.55600000000001</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AC10" s="2">
         <v>173.852</v>
       </c>
-      <c r="AD10" s="3" t="s">
+      <c r="AD10" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="3" t="s">
+      <c r="A11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>22.37</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <v>25.222000000000001</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>47.283000000000001</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <v>39.42</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <v>41.073</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="2">
         <v>32.581000000000003</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="2">
         <v>35.706000000000003</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="2">
         <v>31.408000000000001</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="2">
         <v>39.593000000000004</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11" s="2">
         <v>28.844999999999999</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="2">
         <v>28.64</v>
       </c>
-      <c r="O11" s="3">
+      <c r="O11" s="2">
         <v>25.748000000000001</v>
       </c>
-      <c r="P11" s="3">
+      <c r="P11" s="2">
         <v>35.365000000000002</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="Q11" s="2">
         <v>41.183999999999997</v>
       </c>
-      <c r="R11" s="3">
+      <c r="R11" s="2">
         <v>43.131999999999998</v>
       </c>
-      <c r="S11" s="3">
+      <c r="S11" s="2">
         <v>34.951000000000001</v>
       </c>
-      <c r="T11" s="3">
+      <c r="T11" s="2">
         <v>36.453000000000003</v>
       </c>
-      <c r="U11" s="3">
+      <c r="U11" s="2">
         <v>31.951000000000001</v>
       </c>
-      <c r="V11" s="3">
+      <c r="V11" s="2">
         <v>36.945999999999998</v>
       </c>
-      <c r="W11" s="3">
+      <c r="W11" s="2">
         <v>35.808</v>
       </c>
-      <c r="X11" s="3">
+      <c r="X11" s="2">
         <v>37.494</v>
       </c>
-      <c r="Y11" s="3">
+      <c r="Y11" s="2">
         <v>31.94</v>
       </c>
-      <c r="Z11" s="3">
+      <c r="Z11" s="2">
         <v>26.934000000000001</v>
       </c>
-      <c r="AA11" s="3">
+      <c r="AA11" s="2">
         <v>23.120999999999999</v>
       </c>
-      <c r="AB11" s="3">
+      <c r="AB11" s="2">
         <v>21.306999999999999</v>
       </c>
-      <c r="AC11" s="3">
+      <c r="AC11" s="2">
         <v>20.148</v>
       </c>
-      <c r="AD11" s="3" t="s">
+      <c r="AD11" s="2" t="s">
         <v>33</v>
       </c>
     </row>
